--- a/web/sample/sample_revision.xlsx
+++ b/web/sample/sample_revision.xlsx
@@ -1055,113 +1055,144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
+          <t>주보종명</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
           <t>SP_SPCD</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>개별상품명</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>SP_SPCD1</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>상품명</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>(무)예제건강보험Ⅱ</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>A200</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>(무)예제암진단특약Ⅱ</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>A2001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>(무)예제암진단특약Ⅱ</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>(무)예제건강보험Ⅱ</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>A200</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>(무)예제상해보장특약Ⅱ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>A2002</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>(무)예제상해보장특약Ⅱ</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>(무)예제건강보험Ⅱ</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>A200</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>(무)예제납입면제특약Ⅱ</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>A2003</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>(무)예제납입면제특약Ⅱ</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>(무)예제건강보험Ⅱ</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>A200</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>(무)예제수술특약Ⅱ</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>A2006</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>(무)예제수술특약Ⅱ</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>(무)예제건강보험Ⅱ</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>A200</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>(무)예제간병특약(신규)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>A2008</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>(무)예제간병특약(신규)</t>
         </is>
       </c>
     </row>

--- a/web/sample/sample_revision.xlsx
+++ b/web/sample/sample_revision.xlsx
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>개별상품명</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>SP_SPCD</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>개별상품명</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -1092,14 +1092,14 @@
           <t>(무)예제건강보험Ⅱ</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(무)예제암진단특약Ⅱ</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>A200</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>(무)예제암진단특약Ⅱ</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1114,14 +1114,14 @@
           <t>(무)예제건강보험Ⅱ</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>(무)예제상해보장특약Ⅱ</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>A200</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>(무)예제상해보장특약Ⅱ</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1136,14 +1136,14 @@
           <t>(무)예제건강보험Ⅱ</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>(무)예제납입면제특약Ⅱ</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>A200</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>(무)예제납입면제특약Ⅱ</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1158,14 +1158,14 @@
           <t>(무)예제건강보험Ⅱ</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>(무)예제수술특약Ⅱ</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>A200</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>(무)예제수술특약Ⅱ</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1180,14 +1180,14 @@
           <t>(무)예제건강보험Ⅱ</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>(무)예제간병특약(신규)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>A200</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>(무)예제간병특약(신규)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">

--- a/web/sample/sample_revision.xlsx
+++ b/web/sample/sample_revision.xlsx
@@ -708,8 +708,10 @@
       <c r="E3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -748,8 +750,10 @@
       <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -788,8 +792,10 @@
       <c r="E5" t="n">
         <v>0.2</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -828,8 +834,10 @@
       <c r="E6" t="n">
         <v>0.02</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -868,8 +876,10 @@
       <c r="E7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -908,8 +918,10 @@
       <c r="E8" t="n">
         <v>0.1</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -948,8 +960,10 @@
       <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -988,8 +1002,10 @@
       <c r="E10" t="n">
         <v>1</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -1028,8 +1044,10 @@
       <c r="E11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
